--- a/기타/11.13 2차구매목록_1112.xlsx
+++ b/기타/11.13 2차구매목록_1112.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dbstj\OneDrive\바탕 화면\main_project\SynchroBots_DOC\기타\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2881y\OneDrive\바탕 화면\SynchroBots Project\GIt_SynchroBots\SynchroBots_DOC\기타\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43C4D39-A869-4636-9DBB-57B3E37140FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD89E46-CDF0-4D32-AEBC-FEDE2F318851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{343932E5-CCDF-4074-96BC-E269E36EA69C}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{343932E5-CCDF-4074-96BC-E269E36EA69C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>구매요청 목록</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -158,21 +158,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>헤드렌턴 1,200mA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=1048547&amp;recmYn=N</t>
-  </si>
-  <si>
     <t>LED 하이라이트</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8698545519?itemId=12918597038&amp;vendorItemId=80183246703&amp;q=%ED%95%98%EC%9D%B4%EB%9D%BC%EC%9D%B4%ED%8A%B8+%EC%A1%B0%EB%AA%85&amp;searchId=29f59d5c3577489&amp;sourceType=search&amp;itemsCount=36&amp;searchRank=5&amp;rank=5&amp;traceId=mhu7yvlc</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8492126035?itemId=182439054&amp;vendorItemId=3434578156&amp;q=%ED%95%98%EC%9D%B4%EB%9D%BC%EC%9D%B4%ED%8A%B8+%EC%A1%B0%EB%AA%85&amp;searchId=29f59d5c3577489&amp;sourceType=search&amp;itemsCount=36&amp;searchRank=2&amp;rank=2&amp;traceId=mhu81609</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.devicemart.co.kr/goods/view?no=1324907</t>
   </si>
 </sst>
 </file>
@@ -289,9 +283,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -329,7 +323,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -435,7 +429,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -577,7 +571,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -586,21 +580,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0286A5A-816F-482B-ADB4-3C79FD5C7800}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="66.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14.09765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.59765625" customWidth="1"/>
+    <col min="1" max="1" width="66.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.4140625" customWidth="1"/>
+    <col min="3" max="3" width="14.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.4140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -617,7 +611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -634,7 +628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -651,7 +645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -668,7 +662,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -685,7 +679,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -702,7 +696,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +713,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -736,7 +730,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -753,45 +747,33 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>26</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="1">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E14" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
         <v>27</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1">
-        <v>3000</v>
-      </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>29</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -802,34 +784,20 @@
       <c r="D17" t="s">
         <v>10</v>
       </c>
-      <c r="E17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1">
-        <v>7000</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E17" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="1">
         <f>SUM(C4:C18)</f>
-        <v>189826</v>
+        <v>180226</v>
       </c>
     </row>
   </sheetData>
@@ -840,8 +808,9 @@
     <hyperlink ref="E11" r:id="rId3" display="https://www.devicemart.co.kr/goods/view?no=1341720" xr:uid="{4DBB8A20-02E5-40E2-8479-69935CDC6D8F}"/>
     <hyperlink ref="E12" r:id="rId4" display="https://www.devicemart.co.kr/goods/view?no=1329653" xr:uid="{748C7F04-AEAE-4ADD-937E-7EF494782D17}"/>
     <hyperlink ref="E13" r:id="rId5" xr:uid="{1F7B6B60-6CE1-4A1D-A055-8E8D2F71170F}"/>
+    <hyperlink ref="E17" r:id="rId6" xr:uid="{9FDF4066-2E3C-4AF0-ACBC-732F49791C7E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/기타/11.13 2차구매목록_1112.xlsx
+++ b/기타/11.13 2차구매목록_1112.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2881y\OneDrive\바탕 화면\SynchroBots Project\GIt_SynchroBots\SynchroBots_DOC\기타\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD89E46-CDF0-4D32-AEBC-FEDE2F318851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C05452-D672-49D8-86EA-7F4A6CE3DE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{343932E5-CCDF-4074-96BC-E269E36EA69C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{343932E5-CCDF-4074-96BC-E269E36EA69C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>구매요청 목록</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -62,12 +62,6 @@
   <si>
     <t>다이소몰</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=1030079&amp;recmYn=N</t>
-  </si>
-  <si>
-    <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=1035663&amp;recmYn=N</t>
   </si>
   <si>
     <t>너츠 60fps 스트리밍 웹캠 SC-100</t>
@@ -154,10 +148,6 @@
     <t>https://www.devicemart.co.kr/goods/view?no=15007385</t>
   </si>
   <si>
-    <t>모드버스 어댑터</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>LED 하이라이트</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -166,7 +156,28 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.devicemart.co.kr/goods/view?no=1324907</t>
+    <t>https://item.gmarket.co.kr/Item?spm=gmktpc.searchlist.cpp.d0_0.33771e60pxC0EC&amp;goodscode=4051442991&amp;buyboxtype=ad&amp;utparam-url=%7B%22scene%22%3A%22search%22%2C%22sub_scene%22%3A%22main_srp%22%2C%22x_object_id%22%3A%224051442991%22%2C%22x_object_type%22%3A%22item%22%2C%22x_sku_id%22%3A%220%22%2C%22pageIndex%22%3A%220%22%2C%22pagePos%22%3A%220%22%2C%22pageSize%22%3A%221%22%2C%22listno%22%3A%220%22%2C%22sort%22%3A%22popularity%22%2C%22searchScenario%22%3A%22keyword%22%2C%22query%22%3A%22RS-485%2FEthernet%20%EA%B2%8C%EC%9D%B4%ED%8A%B8%EC%9B%A8%EC%9D%B4%22%2C%22pvid%22%3A%227672da071ef8412fa43f1938c805390d%22%2C%22pvid_sys%22%3A%22gmarket%20server%22%2C%22search_session_id%22%3A%22a6427624-65fe-4e86-86a7-70eef8697953%22%2C%22origin_price%22%3A%2268400%22%2C%22promotion_price%22%3A%2244460%22%2C%22coupon_price%22%3A%2241460%22%2C%22ab_buckets%22%3A%22%22%2C%22trafficType%22%3A%22ad%22%2C%22adProduct%22%3A%22N%22%2C%22adSubProduct%22%3A%22F%22%7D</t>
+  </si>
+  <si>
+    <t>G마켓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>단일 직렬 터미널 Modbus RTU TCP 게이트웨이 산업용 서버 rs485 rj45 이더넷</t>
+  </si>
+  <si>
+    <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=1030079&amp;recmYn=N</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=1035663&amp;recmYn=N</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=1031566&amp;recmYn=N</t>
+  </si>
+  <si>
+    <t>KT CAT7 STP 랜선 케이블 3m</t>
   </si>
 </sst>
 </file>
@@ -176,7 +187,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,6 +229,22 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF161D24"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -247,7 +274,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -261,6 +288,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -579,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0286A5A-816F-482B-ADB4-3C79FD5C7800}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="66.08203125" bestFit="1" customWidth="1"/>
@@ -599,10 +632,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>3</v>
@@ -624,8 +657,8 @@
       <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
+      <c r="E4" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -641,13 +674,13 @@
       <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
+      <c r="E5" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -659,158 +692,177 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5000</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
         <v>78900</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1">
-        <v>38060</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>4686</v>
+        <v>38060</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>5500</v>
+        <v>4686</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>29700</v>
+        <v>5500</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1">
+        <v>29700</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>44460</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1">
-        <v>2400</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
         <v>7980</v>
       </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="E18" s="4"/>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="1">
-        <f>SUM(C4:C18)</f>
-        <v>180226</v>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1">
+        <f>SUM(C4:C19)</f>
+        <v>227286</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E8" r:id="rId1" xr:uid="{01142360-4D6F-47A9-999E-55BBB296544D}"/>
-    <hyperlink ref="E10" r:id="rId2" xr:uid="{3E7362FB-E1FA-40B1-8FB2-DDC28073EB7E}"/>
-    <hyperlink ref="E11" r:id="rId3" display="https://www.devicemart.co.kr/goods/view?no=1341720" xr:uid="{4DBB8A20-02E5-40E2-8479-69935CDC6D8F}"/>
-    <hyperlink ref="E12" r:id="rId4" display="https://www.devicemart.co.kr/goods/view?no=1329653" xr:uid="{748C7F04-AEAE-4ADD-937E-7EF494782D17}"/>
-    <hyperlink ref="E13" r:id="rId5" xr:uid="{1F7B6B60-6CE1-4A1D-A055-8E8D2F71170F}"/>
-    <hyperlink ref="E17" r:id="rId6" xr:uid="{9FDF4066-2E3C-4AF0-ACBC-732F49791C7E}"/>
+    <hyperlink ref="E9" r:id="rId1" xr:uid="{01142360-4D6F-47A9-999E-55BBB296544D}"/>
+    <hyperlink ref="E11" r:id="rId2" xr:uid="{3E7362FB-E1FA-40B1-8FB2-DDC28073EB7E}"/>
+    <hyperlink ref="E12" r:id="rId3" display="https://www.devicemart.co.kr/goods/view?no=1341720" xr:uid="{4DBB8A20-02E5-40E2-8479-69935CDC6D8F}"/>
+    <hyperlink ref="E13" r:id="rId4" display="https://www.devicemart.co.kr/goods/view?no=1329653" xr:uid="{748C7F04-AEAE-4ADD-937E-7EF494782D17}"/>
+    <hyperlink ref="E14" r:id="rId5" xr:uid="{1F7B6B60-6CE1-4A1D-A055-8E8D2F71170F}"/>
+    <hyperlink ref="E18" r:id="rId6" xr:uid="{9FDF4066-2E3C-4AF0-ACBC-732F49791C7E}"/>
+    <hyperlink ref="E4" r:id="rId7" xr:uid="{E9493679-CB2D-4F7B-A673-678C2D68831D}"/>
+    <hyperlink ref="E5" r:id="rId8" xr:uid="{54AD80A5-0CF4-45A2-AFD3-7B9E2F98A71D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>